--- a/Sprint-3/MASTER_BACKUP_SPRINT_3/10_Static_Pages/Static_Pages_Test_Cases.xlsx
+++ b/Sprint-3/MASTER_BACKUP_SPRINT_3/10_Static_Pages/Static_Pages_Test_Cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I22"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -453,10 +453,10 @@
         <v>US Staging (https://mcstaging2.globewest.com/) &amp; AU Staging (https://mcstaging2.globewest.com.au/)</v>
       </c>
       <c r="E2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Authenticate on US Staging with Trade Customer (deepali.londhe@overdose.digital).
-2. Authenticate on AU Staging with Customer (deepalilondhe576@gmail.com).
-3. Navigate to each static page: /terms-and-conditions-page, /privacy-policy, /contact-us, /help-centre, /404.
-4. Verify authenticated session header remains persistent.</v>
+        <v xml:space="preserve">Step 1: Authenticate on US Staging with Trade Customer (trade.tester@globewest.com).
+Step 2: Authenticate on AU Staging with Customer (customer.tester@globewest.com.au).
+Step 3: Navigate to each static page: /terms-and-conditions-page, /privacy-policy, /contact-us, /help-centre, /404.
+Step 4: Verify authenticated session header remains persistent.</v>
       </c>
       <c r="F2" t="str">
         <v>Header persistently displays logged-in user state; Trade pricing and account navigation available across all static pages without session drops.</v>
@@ -485,10 +485,10 @@
         <v>US Staging /terms-and-conditions-page (Desktop 1440x900)</v>
       </c>
       <c r="E3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /terms-and-conditions-page.
-2. Verify presence of "Trade Customers" and "General Public" tabs.
-3. Click into accordion sections (1. Introduction through 16. Definitions).
-4. Assert accordion expands and collapses smoothly.</v>
+        <v xml:space="preserve">Step 1: Navigate to /terms-and-conditions-page.
+Step 2: Verify presence of "Trade Customers" and "General Public" tabs.
+Step 3: Click into accordion sections (1. Introduction through 16. Definitions).
+Step 4: Assert accordion expands and collapses smoothly.</v>
       </c>
       <c r="F3" t="str">
         <v>Interactive tabs toggle between Trade and General Public terms; all 16 numbered sections expand and display clause text clearly.</v>
@@ -517,9 +517,9 @@
         <v>US Staging /terms-and-conditions-page</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect clause 1.1 "Who we are" and contact references.
-2. Check for Australian corporate references (ACN, Victoria, PPSA, claims@globewest.com.au).
-3. Check against US legal requirements.</v>
+        <v xml:space="preserve">Step 1: Inspect clause 1.1 "Who we are" and contact references.
+Step 2: Check for Australian corporate references (ACN, Victoria, PPSA, claims@globewest.com.au).
+Step 3: Check against US legal requirements.</v>
       </c>
       <c r="F4" t="str">
         <v>Terms must specify US legal entity and governing jurisdiction without Australian statutory leakage (ACN, PPSA).</v>
@@ -548,10 +548,10 @@
         <v>Mobile Viewport 390x844 (iPhone 14/15)</v>
       </c>
       <c r="E5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Load /terms-and-conditions-page in mobile viewport.
-2. Verify tab pills wrap cleanly.
-3. Tap to expand accordion items on touch device.
-4. Check horizontal scrolling or layout clipping.</v>
+        <v xml:space="preserve">Step 1: Load /terms-and-conditions-page in mobile viewport.
+Step 2: Verify tab pills wrap cleanly.
+Step 3: Tap to expand accordion items on touch device.
+Step 4: Check horizontal scrolling or layout clipping.</v>
       </c>
       <c r="F5" t="str">
         <v>Accordions stack cleanly; touch targets are minimum 44x44px; zero horizontal scrolling or layout clipping.</v>
@@ -580,9 +580,9 @@
         <v>US Staging /privacy-policy vs AU Baseline /privacy-policy</v>
       </c>
       <c r="E6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /privacy-policy on both environments.
-2. Compare H2 headings: "What we collect", "What we do with information", "Security", "How we use cookies", "List of cookies we collect".
-3. Verify section copy and paragraph counts.</v>
+        <v xml:space="preserve">Step 1: Navigate to /privacy-policy on both environments.
+Step 2: Compare H2 headings: "What we collect", "What we do with information", "Security", "How we use cookies", "List of cookies we collect".
+Step 3: Verify section copy and paragraph counts.</v>
       </c>
       <c r="F6" t="str">
         <v>US Privacy Policy structure, headings, and cookie tables match AU baseline 1-to-1 without content loss.</v>
@@ -611,9 +611,9 @@
         <v>US Staging /privacy-policy (Desktop &amp; Mobile)</v>
       </c>
       <c r="E7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll down to "List of cookies we collect" table.
-2. Inspect table columns: Cookie Name, Cookie Description.
-3. Switch to mobile viewport (390px) and verify table scroll/wrap behavior.</v>
+        <v xml:space="preserve">Step 1: Scroll down to "List of cookies we collect" table.
+Step 2: Inspect table columns: Cookie Name, Cookie Description.
+Step 3: Switch to mobile viewport (390px) and verify table scroll/wrap behavior.</v>
       </c>
       <c r="F7" t="str">
         <v>Cookie table is structured with headers; on mobile, table is horizontally scrollable or responsive without breaking container bounds.</v>
@@ -642,8 +642,8 @@
         <v>US Staging /privacy-policy</v>
       </c>
       <c r="E8" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect Privacy Policy contact section.
-2. Check for Australian ABN and .com.au emails (marketing@globewest.com.au, enquiries@globewest.com.au).</v>
+        <v xml:space="preserve">Step 1: Inspect Privacy Policy contact section.
+Step 2: Check for Australian ABN and .com.au emails (marketing@globewest.com.au, enquiries@globewest.com.au).</v>
       </c>
       <c r="F8" t="str">
         <v>Privacy Policy should list US-appropriate contact endpoints and privacy rights disclosures (e.g., CCPA / US privacy contact).</v>
@@ -672,10 +672,10 @@
         <v>US Staging /contact-us (Desktop 1440x900)</v>
       </c>
       <c r="E9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /contact-us.
-2. Inspect H2 headings ("Contact Us", "Our Showrooms", "Online enquiry").
-3. Test form input fields (Name, Email, Phone, Inquiry Reason, Message).
-4. Attempt submission with empty required fields.</v>
+        <v xml:space="preserve">Step 1: Navigate to /contact-us.
+Step 2: Inspect H2 headings ("Contact Us", "Our Showrooms", "Online enquiry").
+Step 3: Test form input fields (Name, Email, Phone, Inquiry Reason, Message).
+Step 4: Attempt submission with empty required fields.</v>
       </c>
       <c r="F9" t="str">
         <v>Online inquiry form renders cleanly; required field validations trigger with descriptive error messages.</v>
@@ -704,9 +704,9 @@
         <v>US Staging /contact-us</v>
       </c>
       <c r="E10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect "Our Showrooms" section.
-2. Verify showroom cards, addresses, opening hours, and contact emails.
-3. Check whether US showrooms or AU showrooms are displayed.</v>
+        <v xml:space="preserve">Step 1: Inspect "Our Showrooms" section.
+Step 2: Verify showroom cards, addresses, opening hours, and contact emails.
+Step 3: Check whether US showrooms or AU showrooms are displayed.</v>
       </c>
       <c r="F10" t="str">
         <v>US Contact page must display US showroom locations and US contact info.</v>
@@ -735,9 +735,9 @@
         <v>US Staging /contact-us</v>
       </c>
       <c r="E11" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect all showroom and hero image tags in &lt;main&gt;.
-2. Assert naturalWidth &gt; 0 and HTTP 200 for all image assets.
-3. Check for placeholder images.</v>
+        <v xml:space="preserve">Step 1: Inspect all showroom and hero image tags in &lt;main&gt;.
+Step 2: Assert naturalWidth &gt; 0 and HTTP 200 for all image assets.
+Step 3: Check for placeholder images.</v>
       </c>
       <c r="F11" t="str">
         <v>All showroom photos load high-res photography; zero broken image links.</v>
@@ -766,9 +766,9 @@
         <v>Mobile Viewport 390x844</v>
       </c>
       <c r="E12" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Load /contact-us on mobile.
-2. Inspect single-column stacking of form and showroom cards.
-3. Test input tap responsiveness and keyboard avoidance.</v>
+        <v xml:space="preserve">Step 1: Load /contact-us on mobile.
+Step 2: Inspect single-column stacking of form and showroom cards.
+Step 3: Test input tap responsiveness and keyboard avoidance.</v>
       </c>
       <c r="F12" t="str">
         <v>Clean vertical stack; input fields stretch full-width (350px); touch targets conform to mobile accessibility standards.</v>
@@ -797,9 +797,9 @@
         <v>US Staging /help-centre vs AU Baseline /help-centre</v>
       </c>
       <c r="E13" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /help-centre on US Staging.
-2. Inspect document.title via DOM inspection.
-3. Compare with AU baseline document.title.</v>
+        <v xml:space="preserve">Step 1: Navigate to /help-centre on US Staging.
+Step 2: Inspect document.title via DOM inspection.
+Step 3: Compare with AU baseline document.title.</v>
       </c>
       <c r="F13" t="str">
         <v>Document title must be non-empty and descriptive: "&lt;title&gt;Help centre&lt;/title&gt;" (conforms to WCAG 2.2 AA Criterion 2.4.2 Page Titled).</v>
@@ -828,9 +828,9 @@
         <v>US Staging /help-centre</v>
       </c>
       <c r="E14" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect Help Centre hero banner asset.
-2. Inspect category cards (Orders, Delivery, Returns, Trade Accounts, Product Care).
-3. Check category card links and hover states.</v>
+        <v xml:space="preserve">Step 1: Inspect Help Centre hero banner asset.
+Step 2: Inspect category cards (Orders, Delivery, Returns, Trade Accounts, Product Care).
+Step 3: Check category card links and hover states.</v>
       </c>
       <c r="F14" t="str">
         <v>Hero banner renders crisp photography; category cards render with icons and navigate to appropriate articles.</v>
@@ -859,9 +859,9 @@
         <v>Desktop 1440px &amp; Mobile 390px Viewports</v>
       </c>
       <c r="E15" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect search input in Help Centre.
-2. Enter search queries (e.g. "delivery", "trade discount").
-3. Switch to mobile viewport and verify responsive stacking.</v>
+        <v xml:space="preserve">Step 1: Inspect search input in Help Centre.
+Step 2: Enter search queries (e.g. "delivery", "trade discount").
+Step 3: Switch to mobile viewport and verify responsive stacking.</v>
       </c>
       <c r="F15" t="str">
         <v>Search input accessible with placeholder text; category cards stack into 1-2 columns on mobile cleanly.</v>
@@ -890,9 +890,9 @@
         <v>US Staging /non-existent-page-404-test</v>
       </c>
       <c r="E16" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to an arbitrary non-existent URL (/non-existent-page-404-test).
-2. Assert HTTP response status is 404 Not Found.
-3. Verify H2 heading "Page not available." and body copy.</v>
+        <v xml:space="preserve">Step 1: Navigate to an arbitrary non-existent URL (/non-existent-page-404-test).
+Step 2: Assert HTTP response status is 404 Not Found.
+Step 3: Verify H2 heading "Page not available." and body copy.</v>
       </c>
       <c r="F16" t="str">
         <v>Server returns 404 response; user-friendly error message "Page not available." renders within global header and footer.</v>
@@ -921,8 +921,8 @@
         <v>US Staging /non-existent-page-404-test vs AU Baseline</v>
       </c>
       <c r="E17" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Inspect document.title on US 404 page.
-2. Compare with AU baseline title.</v>
+        <v xml:space="preserve">Step 1: Inspect document.title on US 404 page.
+Step 2: Compare with AU baseline title.</v>
       </c>
       <c r="F17" t="str">
         <v>Document title is cleanly formatted: "&lt;title&gt;404 Not Found&lt;/title&gt;".</v>
@@ -951,9 +951,9 @@
         <v>Desktop 1440px &amp; Mobile 390px Viewports</v>
       </c>
       <c r="E18" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Check recovery links (Home, Catalog, Contact Us).
-2. Verify search bar presence in header.
-3. Inspect layout in 390px mobile view.</v>
+        <v xml:space="preserve">Step 1: Check recovery links (Home, Catalog, Contact Us).
+Step 2: Verify search bar presence in header.
+Step 3: Inspect layout in 390px mobile view.</v>
       </c>
       <c r="F18" t="str">
         <v>Header search bar and navigation links allow user recovery; layout renders without distortion on mobile.</v>
@@ -982,9 +982,9 @@
         <v>US Staging Footer Links</v>
       </c>
       <c r="E19" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Click all footer static page links (Terms, Privacy, Contact, FAQ).
-2. Check redirection and URL resolution.
-3. Assert zero 404 errors on linked paths.</v>
+        <v xml:space="preserve">Step 1: Click all footer static page links (Terms, Privacy, Contact, FAQ).
+Step 2: Check redirection and URL resolution.
+Step 3: Assert zero 404 errors on linked paths.</v>
       </c>
       <c r="F19" t="str">
         <v>Footer links map correctly: Terms -&gt; /terms-and-conditions-page, Privacy -&gt; /privacy-policy, Contact -&gt; /contact-us, FAQ -&gt; /help-centre.</v>
@@ -999,9 +999,106 @@
         <v>P1 - High</v>
       </c>
     </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>TC-STAT-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Contact Us Page</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Verify Contact Us Form Input Validation &amp; Error Feedback</v>
+      </c>
+      <c r="D20" t="str">
+        <v>US Staging /contact-us (Desktop &amp; Mobile)</v>
+      </c>
+      <c r="E20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Navigate to /contact-us.
+Step 2: Submit empty contact form.
+Step 3: Verify inline error validation styling.
+Step 4: Fill valid name, email, phone, inquiry type, and message.
+Step 5: Assert submit button interaction.</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Required inputs trigger clear error outlines with accessible text; valid inputs pass client-side validation smoothly.</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Contact form validates required fields cleanly with inline error messaging and proper field labeling.</v>
+      </c>
+      <c r="H20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I20" t="str">
+        <v>P1 - High</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>TC-STAT-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Help Centre / FAQ</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Verify Help Centre FAQ Real-Time Search &amp; Category Filter Traversal</v>
+      </c>
+      <c r="D21" t="str">
+        <v>US Staging /help-centre</v>
+      </c>
+      <c r="E21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Navigate to /help-centre.
+Step 2: Enter keyword search query in FAQ search bar.
+Step 3: Verify real-time accordion filtering.
+Step 4: Click topic category tabs (Orders, Delivery, Returns, Trade Accounts).</v>
+      </c>
+      <c r="F21" t="str">
+        <v>FAQ search dynamically filters questions; topic category tabs switch visible question accordions without layout breakage.</v>
+      </c>
+      <c r="G21" t="str">
+        <v>FAQ topics and accordion questions respond accurately to keyword filtering and category selection.</v>
+      </c>
+      <c r="H21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I21" t="str">
+        <v>P2 - Medium</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>TC-STAT-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>404 Error Page</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Verify 404 Error Page Branded Hero, Search Bar &amp; Home Redirection</v>
+      </c>
+      <c r="D22" t="str">
+        <v>US Staging direct navigation to non-existent route /invalid-page-test-404</v>
+      </c>
+      <c r="E22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Navigate to /non-existent-url-slug.
+Step 2: Verify HTTP 404 status code and branded error layout.
+Step 3: Test "Return to Home" button navigation.
+Step 4: Test embedded search bar execution.</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Branded 404 template renders with helpful navigation, search input, and button redirecting directly to US home page.</v>
+      </c>
+      <c r="G22" t="str">
+        <v>404 page renders branded layout with search bar and functional "Return to Home" button; zero broken asset links.</v>
+      </c>
+      <c r="H22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I22" t="str">
+        <v>P2 - Medium</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I22"/>
   </ignoredErrors>
 </worksheet>
 </file>